--- a/Data/EXCEL/Transfer/salemon/202412/3383-salemon-202412.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202412/3383-salemon-202412.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\202412\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202412\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AECA417-E7FF-418F-B903-B306497A0E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD49DB09-ED7C-4C52-A24A-AC64954AD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{7668763C-DD5E-4734-99D6-3A0662CE4F1C}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="21600" windowHeight="13425" xr2:uid="{05695649-0808-4711-B634-7A729FB25AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="3383-salemon-202412" sheetId="2" r:id="rId1"/>
@@ -1258,23 +1258,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9211CC1-51E2-4279-9767-4D8A2AE7D801}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0568842-3C8A-4FC1-9ABE-E4324F9909DF}">
   <dimension ref="A1:Q18"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="10" width="14.54296875" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" customWidth="1"/>
-    <col min="13" max="13" width="15.26953125" customWidth="1"/>
-    <col min="14" max="15" width="14.54296875" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="9.625" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.625" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="9.625" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="P1" s="20"/>
       <c r="Q1" s="21"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="16" t="s">
         <v>4</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -1383,7 +1383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44835</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>-30.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>44805</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>-31.2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44774</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>44743</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>-30.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44713</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>-28.4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>44682</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>-26.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44652</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>-25.5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>44621</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>-22.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>44593</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>44562</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>-26.4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>44531</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>-7.79</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>44501</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>-4.8499999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>44470</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>-2.0099999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>44440</v>
       </c>
